--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112596</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112596</v>
       </c>
       <c r="B2" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112596</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,430 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126607410</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västra Svalered, Västra Svalered, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>335987</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6435667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126606250</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95604</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västra Svalered, Västra Svalered, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>335992</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6435553</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126605249</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västra Svalered, Västra Svalered, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>336109</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6435506</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126607343</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97241</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västra Svalered, Västra Svalered, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>335968</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6435642</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126607410</v>
+        <v>126606250</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
+        <v>95604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335987</v>
+        <v>335992</v>
       </c>
       <c r="R3" t="n">
-        <v>6435667</v>
+        <v>6435553</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126606250</v>
+        <v>126607410</v>
       </c>
       <c r="B4" t="n">
-        <v>95604</v>
+        <v>8436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335992</v>
+        <v>335987</v>
       </c>
       <c r="R4" t="n">
-        <v>6435553</v>
+        <v>6435667</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126607410</v>
+        <v>126606250</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
+        <v>95679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335987</v>
+        <v>335992</v>
       </c>
       <c r="R3" t="n">
-        <v>6435667</v>
+        <v>6435553</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126606250</v>
+        <v>126607410</v>
       </c>
       <c r="B4" t="n">
-        <v>95604</v>
+        <v>8436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335992</v>
+        <v>335987</v>
       </c>
       <c r="R4" t="n">
-        <v>6435553</v>
+        <v>6435667</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1110,7 +1110,7 @@
         <v>126607343</v>
       </c>
       <c r="B6" t="n">
-        <v>97241</v>
+        <v>97316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126606250</v>
       </c>
       <c r="B3" t="n">
-        <v>95679</v>
+        <v>95685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>126607343</v>
       </c>
       <c r="B6" t="n">
-        <v>97316</v>
+        <v>97322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126606250</v>
+        <v>126607410</v>
       </c>
       <c r="B3" t="n">
-        <v>95685</v>
+        <v>8436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335992</v>
+        <v>335987</v>
       </c>
       <c r="R3" t="n">
-        <v>6435553</v>
+        <v>6435667</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126607410</v>
+        <v>126606250</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>95685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335987</v>
+        <v>335992</v>
       </c>
       <c r="R4" t="n">
-        <v>6435667</v>
+        <v>6435553</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126607410</v>
+        <v>126606250</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
+        <v>95685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335987</v>
+        <v>335992</v>
       </c>
       <c r="R3" t="n">
-        <v>6435667</v>
+        <v>6435553</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126606250</v>
+        <v>126607410</v>
       </c>
       <c r="B4" t="n">
-        <v>95685</v>
+        <v>8436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335992</v>
+        <v>335987</v>
       </c>
       <c r="R4" t="n">
-        <v>6435553</v>
+        <v>6435667</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126606250</v>
       </c>
       <c r="B3" t="n">
-        <v>95685</v>
+        <v>95679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>126607343</v>
       </c>
       <c r="B6" t="n">
-        <v>97322</v>
+        <v>97316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126112596</v>
+        <v>126606250</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lödöse, Vg</t>
+          <t>Västra Svalered, Västra Svalered, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335976</v>
+        <v>335992</v>
       </c>
       <c r="R2" t="n">
-        <v>6435599</v>
+        <v>6435553</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126606250</v>
+        <v>126112596</v>
       </c>
       <c r="B3" t="n">
-        <v>95685</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +793,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Svalered, Västra Svalered, Vg</t>
+          <t>Lödöse, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335992</v>
+        <v>335976</v>
       </c>
       <c r="R3" t="n">
-        <v>6435553</v>
+        <v>6435599</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126607410</v>
+        <v>126605249</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335987</v>
+        <v>336109</v>
       </c>
       <c r="R4" t="n">
-        <v>6435667</v>
+        <v>6435506</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126605249</v>
+        <v>126607410</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>336109</v>
+        <v>335987</v>
       </c>
       <c r="R5" t="n">
-        <v>6435506</v>
+        <v>6435667</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,7 +1110,7 @@
         <v>126607343</v>
       </c>
       <c r="B6" t="n">
-        <v>97322</v>
+        <v>97985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25298-2024 artfynd.xlsx
+++ b/artfynd/A 25298-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126606250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126112596</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126605249</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126607410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,8 +1232,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126607343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>